--- a/seguimiento/matrices/Matriz de roles por operaciones.xlsx
+++ b/seguimiento/matrices/Matriz de roles por operaciones.xlsx
@@ -474,7 +474,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Entregable</t>
+          <t>Entregable (epica / modulo)</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -511,12 +511,12 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Traductor de mensajes</t>
+          <t>Modulo de traduccion de mensajes</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>HU0001</t>
+          <t>HU0001, HU0002</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
@@ -536,12 +536,12 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Traductor de mensajes</t>
+          <t>Modulo de traduccion de mensajes</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>HU0001 (interna)</t>
+          <t>HU0003</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr"/>
@@ -561,12 +561,12 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Configuracion de idiomas</t>
+          <t>Modulo de configuracion de conversacion</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>HU0002</t>
+          <t>HU0006</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -586,12 +586,12 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Configuracion de idiomas</t>
+          <t>Modulo de configuracion de conversacion</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>HU0003</t>
+          <t>HU0007</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr"/>
@@ -611,12 +611,12 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Configuracion de idiomas</t>
+          <t>Modulo de configuracion de conversacion</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>HU0004</t>
+          <t>HU0008</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
@@ -640,12 +640,12 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Gestion de conversaciones</t>
+          <t>Modulo de configuracion de conversacion</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>HU0005</t>
+          <t>HU0009</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
@@ -665,12 +665,12 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Gestion de conversaciones</t>
+          <t>Modulo de configuracion de conversacion</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>HU0006</t>
+          <t>HU0010</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
@@ -690,12 +690,12 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Gestion de conversaciones</t>
+          <t>Modulo de configuracion de conversacion</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>HU0007</t>
+          <t>HU0011</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
@@ -719,12 +719,12 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Historial</t>
+          <t>Modulo de historial de conversaciones</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>HU0008</t>
+          <t>HU0012</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
@@ -744,12 +744,12 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Historial</t>
+          <t>Modulo de historial de conversaciones</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>HU0009</t>
+          <t>HU0013</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
@@ -769,12 +769,12 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Historial</t>
+          <t>Modulo de historial de conversaciones</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>HU0010</t>
+          <t>HU0014</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
@@ -794,12 +794,12 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Historial</t>
+          <t>Modulo de historial de conversaciones</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>HU0011</t>
+          <t>HU0015</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
@@ -819,12 +819,12 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Perfil de usuario</t>
+          <t>Modulo de cuenta de usuario</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>HU0012</t>
+          <t>HU0016</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
@@ -844,12 +844,12 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Perfil de usuario</t>
+          <t>Modulo de cuenta de usuario</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>HU0013</t>
+          <t>HU0017</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
@@ -873,12 +873,12 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Perfil de usuario</t>
+          <t>Modulo de cuenta de usuario</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>HU0014</t>
+          <t>HU0018</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
@@ -902,12 +902,12 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Perfil de usuario</t>
+          <t>Modulo de cuenta de usuario</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>HU0015</t>
+          <t>HU0019</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Audio traducido</t>
+          <t>Modulo de traduccion de mensajes</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>HU0016</t>
+          <t>HU0004</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
@@ -964,12 +964,12 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Audio traducido</t>
+          <t>Modulo de traduccion de mensajes</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>HU0017</t>
+          <t>HU0005</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr"/>
@@ -989,12 +989,12 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Reporte de mala traduccion</t>
+          <t>Modulo de reportes de calidad</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>HU0018</t>
+          <t>HU0022</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
@@ -1014,12 +1014,12 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Participacion en la conversacion</t>
+          <t>Modulo de participacion del interlocutor</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>HU0019</t>
+          <t>HU0020</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr"/>
@@ -1039,12 +1039,12 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Participacion en la conversacion</t>
+          <t>Modulo de participacion del interlocutor</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>HU0020</t>
+          <t>HU0021</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr"/>
@@ -1064,12 +1064,12 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Catalogo de idiomas</t>
+          <t>Modulo de administracion de idiomas y regiones</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>HU0021</t>
+          <t>HU0024, HU0025</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr"/>
@@ -1089,12 +1089,12 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Revision de reportes</t>
+          <t>Modulo de reportes de calidad</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>HU0022</t>
+          <t>HU0023</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr"/>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Analisis de acento y tono</t>
+          <t>Modulo de traduccion de mensajes</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -1139,7 +1139,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Analisis de acento y tono</t>
+          <t>Modulo de traduccion de mensajes</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -1164,7 +1164,7 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Traduccion contextual</t>
+          <t>Modulo de traduccion de mensajes</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">

--- a/seguimiento/matrices/Matriz de roles por operaciones.xlsx
+++ b/seguimiento/matrices/Matriz de roles por operaciones.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Modulo de traduccion de mensajes</t>
+          <t>Traduccion de mensajes</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -536,7 +536,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Modulo de traduccion de mensajes</t>
+          <t>Traduccion de mensajes</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -561,7 +561,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Modulo de configuracion de conversacion</t>
+          <t>Configuracion de conversacion</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -586,7 +586,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Modulo de configuracion de conversacion</t>
+          <t>Configuracion de conversacion</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -611,7 +611,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Modulo de configuracion de conversacion</t>
+          <t>Configuracion de conversacion</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -640,7 +640,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Modulo de configuracion de conversacion</t>
+          <t>Configuracion de conversacion</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Modulo de configuracion de conversacion</t>
+          <t>Configuracion de conversacion</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -690,7 +690,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Modulo de configuracion de conversacion</t>
+          <t>Configuracion de conversacion</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -719,7 +719,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Modulo de historial de conversaciones</t>
+          <t>Historial de conversaciones</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -744,7 +744,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Modulo de historial de conversaciones</t>
+          <t>Historial de conversaciones</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Modulo de historial de conversaciones</t>
+          <t>Historial de conversaciones</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -794,7 +794,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Modulo de historial de conversaciones</t>
+          <t>Historial de conversaciones</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Modulo de cuenta de usuario</t>
+          <t>Cuenta de usuario</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Modulo de cuenta de usuario</t>
+          <t>Cuenta de usuario</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -873,7 +873,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Modulo de cuenta de usuario</t>
+          <t>Cuenta de usuario</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Modulo de cuenta de usuario</t>
+          <t>Cuenta de usuario</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Modulo de traduccion de mensajes</t>
+          <t>Traduccion de mensajes</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Modulo de traduccion de mensajes</t>
+          <t>Traduccion de mensajes</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -989,7 +989,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Modulo de reportes de calidad</t>
+          <t>Reportes de calidad</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Modulo de participacion del interlocutor</t>
+          <t>Participacion del interlocutor</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1039,7 +1039,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Modulo de participacion del interlocutor</t>
+          <t>Participacion del interlocutor</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Modulo de administracion de idiomas y regiones</t>
+          <t>Administracion de idiomas y regiones</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Modulo de reportes de calidad</t>
+          <t>Reportes de calidad</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -1114,7 +1114,7 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Modulo de traduccion de mensajes</t>
+          <t>Traduccion de mensajes</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -1139,7 +1139,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Modulo de traduccion de mensajes</t>
+          <t>Traduccion de mensajes</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -1164,7 +1164,7 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Modulo de traduccion de mensajes</t>
+          <t>Traduccion de mensajes</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">

--- a/seguimiento/matrices/Matriz de roles por operaciones.xlsx
+++ b/seguimiento/matrices/Matriz de roles por operaciones.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Configuracion de conversacion</t>
+          <t>Gestion de conversaciones</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -586,7 +586,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Configuracion de conversacion</t>
+          <t>Gestion de conversaciones</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -611,12 +611,12 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Configuracion de conversacion</t>
+          <t>Administracion de idiomas y regiones</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>HU0008</t>
+          <t>HU0023</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
@@ -640,12 +640,12 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Configuracion de conversacion</t>
+          <t>Gestion de conversaciones</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>HU0009</t>
+          <t>HU0008</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
@@ -665,12 +665,12 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Configuracion de conversacion</t>
+          <t>Gestion de conversaciones</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>HU0010</t>
+          <t>HU0009</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
@@ -690,12 +690,12 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Configuracion de conversacion</t>
+          <t>Gestion de conversaciones</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>HU0011</t>
+          <t>HU0010</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
@@ -719,12 +719,12 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Historial de conversaciones</t>
+          <t>Gestion de conversaciones</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>HU0012</t>
+          <t>HU0011</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
@@ -744,12 +744,12 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Historial de conversaciones</t>
+          <t>Gestion de conversaciones</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>HU0013</t>
+          <t>HU0012</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
@@ -769,12 +769,12 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Historial de conversaciones</t>
+          <t>Gestion de conversaciones</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>HU0014</t>
+          <t>HU0013</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
@@ -794,12 +794,12 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Historial de conversaciones</t>
+          <t>Gestion de conversaciones</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>HU0015</t>
+          <t>HU0014</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>HU0016</t>
+          <t>HU0015</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>HU0017</t>
+          <t>HU0016</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
@@ -878,7 +878,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>HU0018</t>
+          <t>HU0017</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>HU0019</t>
+          <t>HU0018</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
@@ -989,12 +989,12 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Reportes de calidad</t>
+          <t>Reportes</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>HU0022</t>
+          <t>HU0021</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>HU0020</t>
+          <t>HU0019</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr"/>
@@ -1044,7 +1044,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>HU0021</t>
+          <t>HU0020</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr"/>
@@ -1089,12 +1089,12 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Reportes de calidad</t>
+          <t>Reportes</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>HU0023</t>
+          <t>HU0022</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr"/>

--- a/seguimiento/matrices/Matriz de roles por operaciones.xlsx
+++ b/seguimiento/matrices/Matriz de roles por operaciones.xlsx
@@ -454,7 +454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -860,7 +860,7 @@
       <c r="E15" s="3" t="inlineStr"/>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>X</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr"/>
@@ -889,7 +889,7 @@
       <c r="E16" s="3" t="inlineStr"/>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>X</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr"/>
@@ -918,7 +918,7 @@
       <c r="E17" s="3" t="inlineStr"/>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>X</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr"/>
@@ -1176,6 +1176,68 @@
       <c r="E27" s="3" t="inlineStr"/>
       <c r="F27" s="3" t="inlineStr"/>
       <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>Eliminar mi cuenta</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>Cuenta de usuario</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>HU0026</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr"/>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>Renovar la sesion (token de refresco)</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>Cuenta de usuario</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>Sin HU (tecnica)</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr"/>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -1208,14 +1270,14 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>? = pendiente por definir: el modelo de dominio solo tiene la entidad Usuario, no hay una regla que diga si el Administrador inicia sesion con el mismo mecanismo.</t>
+          <t>El Administrador inicia sesion con el mismo mecanismo que el Cliente Traductor (correo y contrasena); su rol lo asigna el sistema.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>El Interlocutor no usa la app: participa desde el dispositivo del Cliente Traductor (por eso no tiene operaciones de cuenta).</t>
+          <t>El Interlocutor no instala la app ni crea cuenta: responde con el celular del Cliente Traductor (se elige "Otra persona"). Por eso no tiene operaciones de cuenta.</t>
         </is>
       </c>
     </row>
